--- a/Employee_Reports_wi48/Errolnil Purificacion Atienza Q0541.xlsx
+++ b/Employee_Reports_wi48/Errolnil Purificacion Atienza Q0541.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-217</v>
+        <v>-220</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-81</v>
+        <v>-84</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-348</v>
+        <v>-351</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-84</v>
+        <v>-87</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1717,9 +1717,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>22-Apr-2025</t>
@@ -1731,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-82</v>
+        <v>-85</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1780,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-83</v>
+        <v>-86</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1829,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1878,11 +1890,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1927,11 +1939,11 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1964,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2013,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2062,11 +2074,11 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2099,11 +2111,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
